--- a/data/primes_standard_cantons_2024.xlsx
+++ b/data/primes_standard_cantons_2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\Documents\GitHub\article-assurance-maladie\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACB593F-FE5C-4F1E-9765-7F5553575FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BA8545-8765-411B-8826-F4E502F0C676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="195" yWindow="660" windowWidth="28485" windowHeight="14970" xr2:uid="{17260124-CA7E-47FB-BFCA-A825969A5E50}"/>
+    <workbookView xWindow="195" yWindow="510" windowWidth="28485" windowHeight="14970" xr2:uid="{17260124-CA7E-47FB-BFCA-A825969A5E50}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -111,10 +111,10 @@
     <t>No canton</t>
   </si>
   <si>
-    <t>primes_standard_canton</t>
-  </si>
-  <si>
     <t>primes_moyennes_assures_canton</t>
+  </si>
+  <si>
+    <t>Prime standard de l'assurance-maladie obligatoire (en francs)</t>
   </si>
 </sst>
 </file>
@@ -167,6 +167,1137 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>No canton</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Feuil1!$A$2:$A$27</c:f>
+              <c:strCache>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>TI</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>GE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>BS</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>NE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>VD</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>JU</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>BL</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>BE</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>SO</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>ZH</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>FR</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>AG</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>SH</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>VS</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>TG</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>SG</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>AR</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>GL</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>LU</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>SZ</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>GR</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>NW</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>OW</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>UR</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>AI</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>ZG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil1!$B$2:$B$27</c:f>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5342-42C8-B407-13083180A73C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Prime standard de l'assurance-maladie obligatoire (en francs)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Feuil1!$A$2:$A$27</c:f>
+              <c:strCache>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>TI</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>GE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>BS</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>NE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>VD</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>JU</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>BL</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>BE</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>SO</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>ZH</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>FR</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>AG</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>SH</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>VS</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>TG</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>SG</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>AR</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>GL</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>LU</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>SZ</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>GR</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>NW</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>OW</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>UR</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>AI</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>ZG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil1!$C$2:$C$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>740.08876379625121</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>730.01442092056027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>693.5173044845759</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>687.30697265177673</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>684.82321427787213</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>668.94455433111318</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>660.61318880146007</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>612.84000728963326</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>602.33143080350078</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>585.7655179913113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>578.18104940687215</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>570.84060152897132</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>569.44987763254505</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>567.5148293804358</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>544.82859876857663</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>540.10611804968573</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>534.27976832274248</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>533.85678859280927</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>532.7765962155836</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>516.95336701352562</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>515.17280288444454</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>494.08807923677301</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>491.60376710274699</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>487.50931198136624</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>441.42162194195447</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>417.85345438068322</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5342-42C8-B407-13083180A73C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="2026104160"/>
+        <c:axId val="2026104640"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2026104160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2026104640"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2026104640"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2026104160"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>400768</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>36931</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>404363</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>89859</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F058FDD-A1EE-6314-DC21-B45FEC7E1563}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -468,6 +1599,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BDE831-4A7B-4B67-8496-6504635DCEE8}">
   <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -477,377 +1611,381 @@
         <v>27</v>
       </c>
       <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
         <v>28</v>
-      </c>
-      <c r="D1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C2">
-        <v>585.7655179913113</v>
+        <v>740.08876379625121</v>
       </c>
       <c r="D2">
-        <v>4168.5134569716474</v>
+        <v>5123.933835951224</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>612.84000728963326</v>
+        <v>730.01442092056027</v>
       </c>
       <c r="D3">
-        <v>4377.5645135358673</v>
+        <v>5365.0107058572157</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>532.7765962155836</v>
+        <v>693.5173044845759</v>
       </c>
       <c r="D4">
-        <v>3645.836820778944</v>
+        <v>5391.0769897103301</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C5">
-        <v>487.50931198136624</v>
+        <v>687.30697265177673</v>
       </c>
       <c r="D5">
-        <v>3256.7216277296434</v>
+        <v>4932.7558673681242</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>516.95336701352562</v>
+        <v>684.82321427787213</v>
       </c>
       <c r="D6">
-        <v>3669.4302839530601</v>
+        <v>4761.9081674760628</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>491.60376710274699</v>
+        <v>668.94455433111318</v>
       </c>
       <c r="D7">
-        <v>3446.760964873904</v>
+        <v>4601.3111707427388</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>494.08807923677301</v>
+        <v>660.61318880146007</v>
       </c>
       <c r="D8">
-        <v>3533.2854216583237</v>
+        <v>4864.2461696416103</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>533.85678859280927</v>
+        <v>612.84000728963326</v>
       </c>
       <c r="D9">
-        <v>3761.1541014731092</v>
+        <v>4377.5645135358673</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>417.85345438068322</v>
+        <v>602.33143080350078</v>
       </c>
       <c r="D10">
-        <v>3524.7812456383094</v>
+        <v>4294.1276558075497</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>578.18104940687215</v>
+        <v>585.7655179913113</v>
       </c>
       <c r="D11">
-        <v>4013.7776997543115</v>
+        <v>4168.5134569716474</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>602.33143080350078</v>
+        <v>578.18104940687215</v>
       </c>
       <c r="D12">
-        <v>4294.1276558075497</v>
+        <v>4013.7776997543115</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C13">
-        <v>693.5173044845759</v>
+        <v>570.84060152897132</v>
       </c>
       <c r="D13">
-        <v>5391.0769897103301</v>
+        <v>3948.1822615417741</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14">
-        <v>660.61318880146007</v>
+        <v>569.44987763254505</v>
       </c>
       <c r="D14">
-        <v>4864.2461696416103</v>
+        <v>4193.5672491904143</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C15">
-        <v>569.44987763254505</v>
+        <v>567.5148293804358</v>
       </c>
       <c r="D15">
-        <v>4193.5672491904143</v>
+        <v>3970.3646329311873</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C16">
-        <v>534.27976832274248</v>
+        <v>544.82859876857663</v>
       </c>
       <c r="D16">
-        <v>3720.2796050898032</v>
+        <v>3842.0724086559248</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17">
-        <v>441.42162194195447</v>
+        <v>540.10611804968573</v>
       </c>
       <c r="D17">
-        <v>2933.0270341609357</v>
+        <v>3784.3767298850271</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C18">
-        <v>540.10611804968573</v>
+        <v>534.27976832274248</v>
       </c>
       <c r="D18">
-        <v>3784.3767298850271</v>
+        <v>3720.2796050898032</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>515.17280288444454</v>
+        <v>533.85678859280927</v>
       </c>
       <c r="D19">
-        <v>3751.3448470185403</v>
+        <v>3761.1541014731092</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B20">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>570.84060152897132</v>
+        <v>532.7765962155836</v>
       </c>
       <c r="D20">
-        <v>3948.1822615417741</v>
+        <v>3645.836820778944</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B21">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>544.82859876857663</v>
+        <v>516.95336701352562</v>
       </c>
       <c r="D21">
-        <v>3842.0724086559248</v>
+        <v>3669.4302839530601</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B22">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C22">
-        <v>740.08876379625121</v>
+        <v>515.17280288444454</v>
       </c>
       <c r="D22">
-        <v>5123.933835951224</v>
+        <v>3751.3448470185403</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B23">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C23">
-        <v>684.82321427787213</v>
+        <v>494.08807923677301</v>
       </c>
       <c r="D23">
-        <v>4761.9081674760628</v>
+        <v>3533.2854216583237</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B24">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>567.5148293804358</v>
+        <v>491.60376710274699</v>
       </c>
       <c r="D24">
-        <v>3970.3646329311873</v>
+        <v>3446.760964873904</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B25">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C25">
-        <v>687.30697265177673</v>
+        <v>487.50931198136624</v>
       </c>
       <c r="D25">
-        <v>4932.7558673681242</v>
+        <v>3256.7216277296434</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B26">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C26">
-        <v>730.01442092056027</v>
+        <v>441.42162194195447</v>
       </c>
       <c r="D26">
-        <v>5365.0107058572157</v>
+        <v>2933.0270341609357</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B27">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C27">
-        <v>668.94455433111318</v>
+        <v>417.85345438068322</v>
       </c>
       <c r="D27">
-        <v>4601.3111707427388</v>
+        <v>3524.7812456383094</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D27">
+    <sortCondition descending="1" ref="C2:C27"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>